--- a/TDXapp/tdxAppData/akEMPB.xlsx
+++ b/TDXapp/tdxAppData/akEMPB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>000851</t>
+          <t>399415</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>931852</t>
+          <t>H30082</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>988106</t>
+          <t>H30083</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>000858</t>
+          <t>931852</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>000854</t>
+          <t>H11136</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>000847</t>
+          <t>399679</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H30537</t>
+          <t>399416</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>988201</t>
+          <t>H11121</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>000170</t>
+          <t>931127</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>399416</t>
+          <t>H30537</t>
         </is>
       </c>
     </row>
@@ -541,167 +541,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>399679</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>000849</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>988107</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>000865</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>H30082</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>931127</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>932307</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>988007</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>000857</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>H30083</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>932258</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
           <t>H30373</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>988006</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>H11136</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>H11121</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>399415</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>000856</t>
         </is>
       </c>
     </row>
